--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.008438437034621818</v>
       </c>
       <c r="C2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>31660384</v>
+        <v>4133170</v>
       </c>
       <c r="L2" t="n">
-        <v>17749876</v>
+        <v>2066052</v>
       </c>
       <c r="M2" t="n">
-        <v>4281987</v>
+        <v>461424</v>
       </c>
       <c r="N2" t="n">
-        <v>132179</v>
+        <v>11620</v>
       </c>
       <c r="O2" t="n">
-        <v>2579088</v>
+        <v>292654</v>
       </c>
       <c r="P2" t="n">
-        <v>906789</v>
+        <v>107406</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9999390244483948</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8791078925132751</v>
+        <v>0.8017667531967163</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7717258930206299</v>
+        <v>0.6302735805511475</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7099983096122742</v>
+        <v>0.5344378352165222</v>
       </c>
       <c r="U2" t="n">
-        <v>0.254403680562973</v>
+        <v>0.1596987396478653</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7386599183082581</v>
+        <v>0.5878687500953674</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8578211665153503</v>
+        <v>0.7200289368629456</v>
       </c>
       <c r="X2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="AG2" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AH2" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AI2" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563413858413696</v>
+        <v>0.9555707573890686</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113937020301819</v>
+        <v>0.9118538498878479</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582093119621277</v>
+        <v>0.8584820032119751</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620789766311646</v>
+        <v>0.6613538861274719</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020217657089233</v>
+        <v>0.9020804166793823</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00202340465893989</v>
       </c>
       <c r="C3" t="n">
-        <v>2534</v>
+        <v>362</v>
       </c>
       <c r="D3" t="n">
-        <v>31660384</v>
+        <v>4133170</v>
       </c>
       <c r="E3" t="n">
-        <v>3412530</v>
+        <v>835251</v>
       </c>
       <c r="F3" t="n">
-        <v>66592</v>
+        <v>26519</v>
       </c>
       <c r="G3" t="n">
-        <v>4907</v>
+        <v>1718</v>
       </c>
       <c r="H3" t="n">
-        <v>4254</v>
+        <v>2059</v>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="J3" t="n">
-        <v>70113659</v>
+        <v>10016237</v>
       </c>
       <c r="K3" t="n">
-        <v>74802076</v>
+        <v>10308551</v>
       </c>
       <c r="L3" t="n">
-        <v>86168890</v>
+        <v>11830109</v>
       </c>
       <c r="M3" t="n">
-        <v>106025327</v>
+        <v>14991093</v>
       </c>
       <c r="N3" t="n">
-        <v>113295360</v>
+        <v>16178994</v>
       </c>
       <c r="O3" t="n">
-        <v>109828464</v>
+        <v>15613990</v>
       </c>
       <c r="P3" t="n">
-        <v>112803373</v>
+        <v>16094330</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9006891250610352</v>
+        <v>0.8267760276794434</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7755117416381836</v>
+        <v>0.628453254699707</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6554518342018127</v>
+        <v>0.4926853775978088</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2116709798574448</v>
+        <v>0.1298846453428268</v>
       </c>
       <c r="V3" t="n">
-        <v>0.723193883895874</v>
+        <v>0.5733344554901123</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6699427962303162</v>
+        <v>0.5550497174263</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="Z3" t="n">
-        <v>1384204</v>
+        <v>196812</v>
       </c>
       <c r="AA3" t="n">
-        <v>59560</v>
+        <v>8425</v>
       </c>
       <c r="AB3" t="n">
-        <v>47621</v>
+        <v>6828</v>
       </c>
       <c r="AC3" t="n">
-        <v>247</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70116354</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>77619300</v>
+        <v>11107886</v>
       </c>
       <c r="AG3" t="n">
-        <v>89394449</v>
+        <v>12753027</v>
       </c>
       <c r="AH3" t="n">
-        <v>106848837</v>
+        <v>15260727</v>
       </c>
       <c r="AI3" t="n">
-        <v>113471912</v>
+        <v>16209880</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110391725</v>
+        <v>15769225</v>
       </c>
       <c r="AK3" t="n">
-        <v>112860888</v>
+        <v>16122838</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575594067573547</v>
+        <v>0.9575715065002441</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099474549293518</v>
+        <v>0.9095625281333923</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574531674385071</v>
+        <v>0.8570923805236816</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6615032553672791</v>
+        <v>0.6604667901992798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015399217605591</v>
+        <v>0.9011915326118469</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4082097</v>
+        <v>955281</v>
       </c>
       <c r="E4" t="n">
-        <v>17749876</v>
+        <v>2066052</v>
       </c>
       <c r="F4" t="n">
-        <v>937229</v>
+        <v>223540</v>
       </c>
       <c r="G4" t="n">
-        <v>31492</v>
+        <v>10027</v>
       </c>
       <c r="H4" t="n">
-        <v>81076</v>
+        <v>29949</v>
       </c>
       <c r="I4" t="n">
-        <v>6183</v>
+        <v>2670</v>
       </c>
       <c r="J4" t="n">
-        <v>2695</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>4353835</v>
+        <v>1021908</v>
       </c>
       <c r="L4" t="n">
-        <v>5250357</v>
+        <v>1211972</v>
       </c>
       <c r="M4" t="n">
-        <v>1748995</v>
+        <v>401958</v>
       </c>
       <c r="N4" t="n">
-        <v>387385</v>
+        <v>61142</v>
       </c>
       <c r="O4" t="n">
-        <v>912489</v>
+        <v>205168</v>
       </c>
       <c r="P4" t="n">
-        <v>150295</v>
+        <v>41763</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999695420265198</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8897676467895508</v>
+        <v>0.8140794038772583</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7736141681671143</v>
+        <v>0.6293621063232422</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6816355586051941</v>
+        <v>0.5127130150794983</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2310783267021179</v>
+        <v>0.1432569324970245</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7308451533317566</v>
+        <v>0.580510675907135</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7523297071456909</v>
+        <v>0.6268662214279175</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1434717</v>
+        <v>207948</v>
       </c>
       <c r="Z4" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AA4" t="n">
-        <v>579437</v>
+        <v>82633</v>
       </c>
       <c r="AB4" t="n">
-        <v>38501</v>
+        <v>5536</v>
       </c>
       <c r="AC4" t="n">
-        <v>7988</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1536611</v>
+        <v>222573</v>
       </c>
       <c r="AG4" t="n">
-        <v>2024798</v>
+        <v>289054</v>
       </c>
       <c r="AH4" t="n">
-        <v>925485</v>
+        <v>132324</v>
       </c>
       <c r="AI4" t="n">
-        <v>210833</v>
+        <v>30256</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349228</v>
+        <v>49933</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569499492645264</v>
+        <v>0.9565700888633728</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106699824333191</v>
+        <v>0.9107067584991455</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578310608863831</v>
+        <v>0.8577865958213806</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617910265922546</v>
+        <v>0.6609100103378296</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017807841300964</v>
+        <v>0.9016357064247131</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>180236</v>
+        <v>47446</v>
       </c>
       <c r="E5" t="n">
-        <v>1571553</v>
+        <v>306994</v>
       </c>
       <c r="F5" t="n">
-        <v>4281987</v>
+        <v>461424</v>
       </c>
       <c r="G5" t="n">
-        <v>112941</v>
+        <v>20515</v>
       </c>
       <c r="H5" t="n">
-        <v>358255</v>
+        <v>90337</v>
       </c>
       <c r="I5" t="n">
-        <v>27906</v>
+        <v>9833</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3490905</v>
+        <v>865971</v>
       </c>
       <c r="L5" t="n">
-        <v>5138077</v>
+        <v>1221467</v>
       </c>
       <c r="M5" t="n">
-        <v>2250891</v>
+        <v>475125</v>
       </c>
       <c r="N5" t="n">
-        <v>492276</v>
+        <v>77844</v>
       </c>
       <c r="O5" t="n">
-        <v>987159</v>
+        <v>217788</v>
       </c>
       <c r="P5" t="n">
-        <v>446743</v>
+        <v>86101</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999763965606689</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9313714504241943</v>
+        <v>0.8843891620635986</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9091182947158813</v>
+        <v>0.8509798645973206</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9650076031684875</v>
+        <v>0.9462887644767761</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9923043847084045</v>
+        <v>0.9914886951446533</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9833812117576599</v>
+        <v>0.974098801612854</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9947769045829773</v>
+        <v>0.9921697974205017</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56186</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>596891</v>
+        <v>86001</v>
       </c>
       <c r="AA5" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AB5" t="n">
-        <v>69704</v>
+        <v>9990</v>
       </c>
       <c r="AC5" t="n">
-        <v>204029</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1491842</v>
+        <v>212106</v>
       </c>
       <c r="AG5" t="n">
-        <v>2061119</v>
+        <v>297315</v>
       </c>
       <c r="AH5" t="n">
-        <v>931241</v>
+        <v>133840</v>
       </c>
       <c r="AI5" t="n">
-        <v>211376</v>
+        <v>30376</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351133</v>
+        <v>50436</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735060334205627</v>
+        <v>0.9733809232711792</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642549753189087</v>
+        <v>0.9640916585922241</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837567210197449</v>
+        <v>0.9837005138397217</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963063597679138</v>
+        <v>0.9962869882583618</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938730001449585</v>
+        <v>0.9938535690307617</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983745217323303</v>
+        <v>0.9983724355697632</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>86388</v>
+        <v>16169</v>
       </c>
       <c r="E6" t="n">
-        <v>137798</v>
+        <v>21830</v>
       </c>
       <c r="F6" t="n">
-        <v>198702</v>
+        <v>26768</v>
       </c>
       <c r="G6" t="n">
-        <v>132179</v>
+        <v>11620</v>
       </c>
       <c r="H6" t="n">
-        <v>65309</v>
+        <v>11826</v>
       </c>
       <c r="I6" t="n">
-        <v>3934</v>
+        <v>1230</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45337</v>
+        <v>6558</v>
       </c>
       <c r="Z6" t="n">
-        <v>37466</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>76329</v>
+        <v>10994</v>
       </c>
       <c r="AB6" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AC6" t="n">
-        <v>48877</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4760</v>
+        <v>2923</v>
       </c>
       <c r="E7" t="n">
-        <v>120489</v>
+        <v>44238</v>
       </c>
       <c r="F7" t="n">
-        <v>521794</v>
+        <v>116317</v>
       </c>
       <c r="G7" t="n">
-        <v>227932</v>
+        <v>26342</v>
       </c>
       <c r="H7" t="n">
-        <v>2579088</v>
+        <v>292654</v>
       </c>
       <c r="I7" t="n">
-        <v>112184</v>
+        <v>27968</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>5670</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207844</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53148</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>89</v>
       </c>
       <c r="E8" t="n">
-        <v>7987</v>
+        <v>3659</v>
       </c>
       <c r="F8" t="n">
-        <v>24678</v>
+        <v>8814</v>
       </c>
       <c r="G8" t="n">
-        <v>10113</v>
+        <v>2540</v>
       </c>
       <c r="H8" t="n">
-        <v>403595</v>
+        <v>70997</v>
       </c>
       <c r="I8" t="n">
-        <v>906789</v>
+        <v>107406</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
